--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XI-XX/FRACC XVI/LTAIPT_A63F16B.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="58">
   <si>
     <t>48965</t>
   </si>
@@ -158,7 +158,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
@@ -170,22 +170,19 @@
     <t>05/04/2018</t>
   </si>
   <si>
-    <t>AEBF8D608D6B9C6D61B0B1A128BCC43D</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>03/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de julio de 2022 al 30 de septiembre de 2022,  el Colegio de Bachilleres del Estado de Tlaxcala, no asigna recursos públicos a personas físicas o morales, nacionales y/o extranjeras, incluso a los sindicatos y a las personas físicas o morales que realicen actos de autoridad bajo designación presupuestal especial y específica o por cualquier otro motivo, apegándose únicamente a los conceptos establecidos en las Condiciones Generales de Trabajo y Contrato Colectivo de Trabajo, en este sentido al no existir información qué publicar, no se establece un hipervínculo de los programas con objetivos y metas.</t>
-  </si>
-  <si>
-    <t>C6E259A9ACCC85EE594812DC204B7F36</t>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>540831BF75AB8D2808E0BA107E4F6D8A</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>02/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2023 al 30 de septiembre de 2023,  el Colegio de Bachilleres del Estado de Tlaxcala, no asigna recursos públicos a personas físicas o morales, nacionales y/o extranjeras, incluso a los sindicatos que realicen actos de autoridad bajo designación presupuestal especial y específica o por cualquier otro motivo, apegándose únicamente a los conceptos establecidos en las Condiciones Generales de Trabajo y Contrato Colectivo de Trabajo, en este sentido al no existir información qué publicar, no se ha modificado la fecha de actualización y en su caso establecer un hipervínculo de los programas con objetivos y metas.</t>
   </si>
   <si>
     <t>Efectivo</t>
@@ -271,15 +268,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -590,10 +584,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -618,36 +612,36 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="4" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4" t="s">
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
@@ -750,25 +744,25 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
     </row>
     <row r="7" spans="1:17" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
@@ -822,13 +816,13 @@
     </row>
     <row r="8" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>52</v>
@@ -869,60 +863,7 @@
       <c r="P8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q9" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>54</v>
       </c>
     </row>
@@ -937,7 +878,7 @@
     <mergeCell ref="G3:I3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E192">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E196">
       <formula1>Hidden_14</formula1>
     </dataValidation>
   </dataValidations>
@@ -952,17 +893,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
